--- a/Oct - 05/Morning/Morning_OOS_Summary_2026-10-05.xlsx
+++ b/Oct - 05/Morning/Morning_OOS_Summary_2026-10-05.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -512,12 +512,12 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Total Outlets: 15</t>
+          <t>Total Outlets: 20</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Total Items with OOS: 41</t>
+          <t>Total Items with OOS: 44</t>
         </is>
       </c>
       <c r="E1" s="2" t="n"/>
@@ -852,7 +852,7 @@
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>KA-BLR-Cloud FC Malleshwaram</t>
+          <t>KA-BLR-Cloud FC Basaveshwara Nagar</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -861,34 +861,40 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Assorted Cheesecakes (Pack Of 6)</t>
+          <t>Assorted French Macarons (Pack Of 5)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
+      <c r="A15" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>KA-BLR-Cloud FC Electronic City</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
+          <t>Signature Belgium Chocolate Medovik With Macaron</t>
         </is>
       </c>
     </row>
@@ -907,40 +913,34 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Danish Hazelnut Chocolate Medovik With Macaron</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>KA-BLR-Cloud FC Whitefield</t>
-        </is>
-      </c>
+      <c r="D17" s="8" t="inlineStr"/>
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 12)</t>
+          <t>Pack Of 4 Medoviks And 4 Macarons</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>KA-BLR-Ivory Lounge JP Nagar</t>
+          <t>KA-BLR-Cloud FC Malleshwaram</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
@@ -969,7 +969,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 5)</t>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
@@ -984,142 +984,148 @@
       <c r="D19" s="8" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Italian Tiramisu Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>KA-BLR-Cloud FC Sarjapur</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>KA-BLR-Ivory Lounge JP Nagar</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F22" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>HYD</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>TG-HYD-Cloud FC Attapur</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Assorted Cheesecakes (Pack Of 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="8" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Lotus Biscoff Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Cloud FC Charminar</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="4" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="8" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>11</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1138,67 +1144,67 @@
       <c r="D25" s="8" t="inlineStr"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Lotus Biscoff Cheesecake With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Cloud FC Charminar</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Lotus Biscoff Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="4" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="8" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="F26" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Assorted Cheesecakes (Pack Of 12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Cloud FC Habsiguda</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="F27" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
@@ -1217,11 +1223,11 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Assorted Cheesecakes (Pack Of 6)</t>
+          <t>Lotus Biscoff Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
@@ -1240,17 +1246,17 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Assorted Cheesecakes (Pack Of 12)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -1260,7 +1266,7 @@
       <c r="C30" s="4" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TG-HYD-Express Outlet Madhapur</t>
+          <t>TG-HYD-Cloud FC Habsiguda</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -1269,194 +1275,206 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="4" t="n">
-        <v>11</v>
-      </c>
+      <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Express Outlet Manikonda</t>
-        </is>
-      </c>
+      <c r="D31" s="8" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
           <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Express Outlet Sainikpuri</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Express Outlet Madhapur</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Italian Tiramisu Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Express Outlet Manikonda</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Express Outlet Sainikpuri</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>MUM</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>MH-MUM-Cloud FC BKC</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>MH-MUM-Cloud FC Borivali</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Pack Of 4 Medoviks And 4 Macarons</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Assorted French Macarons (Pack Of 5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Assorted French Macarons (Pack Of 12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Signature Belgium Chocolate Medovik With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
         </is>
       </c>
     </row>
@@ -1475,34 +1493,40 @@
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Danish Hazelnut Chocolate Medovik With Macaron</t>
+          <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="4" t="inlineStr"/>
+      <c r="A39" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="8" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>MH-MUM-Cloud FC Chembur</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Assorted French Macarons (Pack Of 5)</t>
         </is>
       </c>
     </row>
@@ -1521,11 +1545,11 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Harley's Spl. Classic Russian Medovik With Macaron</t>
+          <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
       </c>
     </row>
@@ -1544,71 +1568,146 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Pack Of 4 Medoviks And 4 Macarons</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="8" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Pack Of 9 Medoviks And 6 Macarons</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>MH-MUM-Express Outlet Jio World</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Italian Tiramisu Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>MH-MUM-Express Outlet Palladium</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Italian Cappuccino</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>PUN</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>MH-PUN-Cloud FC Tathewadi</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>MH-MUM-Express Outlet Jio World</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>PUN</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>MH-PUN-Cloud FC Tathewadi</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>Harley's Special Mawa Bar Cake (250 Gms)</t>
         </is>
@@ -1929,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1950,12 +2049,12 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Total Outlets: 4</t>
+          <t>Total Outlets: 6</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Total Items with OOS: 8</t>
+          <t>Total Items with OOS: 12</t>
         </is>
       </c>
       <c r="E1" s="2" t="n"/>
@@ -2067,7 +2166,7 @@
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>KA-BLR-Cloud FC Malleshwaram</t>
+          <t>KA-BLR-Cloud FC Basaveshwara Nagar</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -2076,34 +2175,40 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Assorted Cheesecakes (Pack Of 6)</t>
+          <t>Assorted French Macarons (Pack Of 5)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr"/>
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>KA-BLR-Cloud FC Electronic City</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
+          <t>Signature Belgium Chocolate Medovik With Macaron</t>
         </is>
       </c>
     </row>
@@ -2122,40 +2227,34 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Danish Hazelnut Chocolate Medovik With Macaron</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="A8" s="4" t="inlineStr"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>KA-BLR-Cloud FC Whitefield</t>
-        </is>
-      </c>
+      <c r="D8" s="8" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 12)</t>
+          <t>Pack Of 4 Medoviks And 4 Macarons</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2270,12 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>KA-BLR-Ivory Lounge JP Nagar</t>
+          <t>KA-BLR-Cloud FC Malleshwaram</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
@@ -2184,7 +2283,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 5)</t>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
@@ -2199,13 +2298,117 @@
       <c r="D10" s="8" t="inlineStr"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Italian Tiramisu Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>KA-BLR-Cloud FC Sarjapur</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>KA-BLR-Ivory Lounge JP Nagar</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F13" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
@@ -2222,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2248,7 +2451,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Total Items with OOS: 13</t>
+          <t>Total Items with OOS: 12</t>
         </is>
       </c>
       <c r="E1" s="2" t="n"/>
@@ -2317,11 +2520,11 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Assorted Cheesecakes (Pack Of 6)</t>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
@@ -2340,63 +2543,63 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
+          <t>Lotus Biscoff Cheesecake With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Cloud FC Charminar</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
           <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Lotus Biscoff Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Cloud FC Charminar</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
         </is>
       </c>
     </row>
@@ -2415,11 +2618,11 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Lotus Biscoff Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
@@ -2438,63 +2641,63 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Lotus Biscoff Cheesecake With Macaron</t>
+          <t>Assorted Cheesecakes (Pack Of 12)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Cloud FC Habsiguda</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Assorted Cheesecakes (Pack Of 12)</t>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="A10" s="4" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Cloud FC Habsiguda</t>
-        </is>
-      </c>
+      <c r="D10" s="8" t="inlineStr"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
@@ -2513,40 +2716,46 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Assorted Cheesecakes (Pack Of 6)</t>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="inlineStr"/>
+      <c r="A12" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Express Outlet Madhapur</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Italian Tiramisu Medovik With Macaron</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2556,7 +2765,7 @@
       <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TG-HYD-Express Outlet Madhapur</t>
+          <t>TG-HYD-Express Outlet Manikonda</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2565,17 +2774,17 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2585,47 +2794,18 @@
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TG-HYD-Express Outlet Manikonda</t>
+          <t>TG-HYD-Express Outlet Sainikpuri</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Express Outlet Sainikpuri</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
@@ -2663,7 +2843,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Total Outlets: 2</t>
+          <t>Total Outlets: 5</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -2728,32 +2908,38 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
+          <t>MH-MUM-Cloud FC BKC</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
           <t>MH-MUM-Cloud FC Borivali</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Pack Of 4 Medoviks And 4 Macarons</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
@@ -2792,25 +2978,31 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr"/>
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>MH-MUM-Cloud FC Chembur</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Signature Belgium Chocolate Medovik With Macaron</t>
+          <t>Assorted French Macarons (Pack Of 5)</t>
         </is>
       </c>
     </row>
@@ -2829,11 +3021,11 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
+          <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
       </c>
     </row>
@@ -2852,11 +3044,11 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Danish Hazelnut Chocolate Medovik With Macaron</t>
+          <t>Pack Of 4 Medoviks And 4 Macarons</t>
         </is>
       </c>
     </row>
@@ -2875,11 +3067,11 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
         </is>
       </c>
     </row>
@@ -2898,40 +3090,46 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Harley's Spl. Classic Russian Medovik With Macaron</t>
+          <t>Pack Of 9 Medoviks And 6 Macarons</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="inlineStr"/>
+      <c r="A11" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>MH-MUM-Express Outlet Jio World</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+          <t>Italian Tiramisu Medovik With Macaron</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -2941,7 +3139,7 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>MH-MUM-Express Outlet Jio World</t>
+          <t>MH-MUM-Express Outlet Palladium</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2950,11 +3148,11 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
+          <t>Italian Cappuccino</t>
         </is>
       </c>
     </row>

--- a/Oct - 05/Morning/Morning_OOS_Summary_2026-10-05.xlsx
+++ b/Oct - 05/Morning/Morning_OOS_Summary_2026-10-05.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -512,12 +512,12 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Total Outlets: 20</t>
+          <t>Total Outlets: 18</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Total Items with OOS: 44</t>
+          <t>Total Items with OOS: 49</t>
         </is>
       </c>
       <c r="E1" s="2" t="n"/>
@@ -852,12 +852,12 @@
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>KA-BLR-Cloud FC Basaveshwara Nagar</t>
+          <t>KA-BLR-Cloud FC Bellandur</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
@@ -865,36 +865,30 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 5)</t>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>KA-BLR-Cloud FC Electronic City</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Signature Belgium Chocolate Medovik With Macaron</t>
+          <t>Assorted Medoviks (Pack Of 6)</t>
         </is>
       </c>
     </row>
@@ -909,15 +903,15 @@
       <c r="D16" s="8" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Danish Hazelnut Chocolate Medovik With Macaron</t>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
         </is>
       </c>
     </row>
@@ -932,67 +926,67 @@
       <c r="D17" s="8" t="inlineStr"/>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
+          <t>Harley's Signatures (Pack of 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
           <t>Pack Of 4 Medoviks And 4 Macarons</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="6" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>KA-BLR-Cloud FC Malleshwaram</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Assorted Cheesecakes (Pack Of 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
         </is>
       </c>
     </row>
@@ -1011,46 +1005,40 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Italian Tiramisu Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>KA-BLR-Cloud FC Sarjapur</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -1060,39 +1048,45 @@
       <c r="C22" s="4" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>KA-BLR-Ivory Lounge JP Nagar</t>
+          <t>KA-BLR-Cloud FC Nagawara</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 5)</t>
+          <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="4" t="inlineStr"/>
+      <c r="A23" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="8" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>KA-BLR-Cloud FC Whitefield</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -1102,34 +1096,30 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>HYD</t>
-        </is>
-      </c>
+      <c r="C24" s="4" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TG-HYD-Cloud FC Attapur</t>
+          <t>KA-BLR-Ivory Lounge JP Nagar</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Assorted French Macarons (Pack Of 5)</t>
         </is>
       </c>
     </row>
@@ -1144,44 +1134,48 @@
       <c r="D25" s="8" t="inlineStr"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Lotus Biscoff Cheesecake With Macaron</t>
+          <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>HYD</t>
+        </is>
+      </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TG-HYD-Cloud FC Charminar</t>
+          <t>TG-HYD-Cloud FC Attapur</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
@@ -1196,11 +1190,11 @@
       <c r="D27" s="8" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
@@ -1219,63 +1213,63 @@
       <c r="D28" s="8" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Lotus Biscoff Cheesecake With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Cloud FC Charminar</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Lotus Biscoff Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="F29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Assorted Cheesecakes (Pack Of 12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Cloud FC Habsiguda</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="F30" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1298,11 +1292,11 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Assorted Cheesecakes (Pack Of 6)</t>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
@@ -1321,46 +1315,40 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Lotus Biscoff Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>12</v>
-      </c>
+      <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Express Outlet Madhapur</t>
-        </is>
-      </c>
+      <c r="D33" s="8" t="inlineStr"/>
       <c r="E33" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
+          <t>Assorted Cheesecakes (Pack Of 12)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -1370,7 +1358,7 @@
       <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TG-HYD-Express Outlet Manikonda</t>
+          <t>TG-HYD-Cloud FC Habsiguda</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1379,79 +1367,63 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="8" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
           <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Express Outlet Sainikpuri</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Assorted French Macarons (Pack Of 12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>MUM</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>MH-MUM-Cloud FC BKC</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Assorted French Macarons (Pack Of 24)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -1461,7 +1433,7 @@
       <c r="C37" s="4" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>MH-MUM-Cloud FC Borivali</t>
+          <t>TG-HYD-Express Outlet Kapil Tower</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -1470,40 +1442,46 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 5)</t>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="4" t="inlineStr"/>
+      <c r="A38" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="8" t="inlineStr"/>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Express Outlet Madhapur</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 12)</t>
+          <t>Italian Tiramisu Medovik With Macaron</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -1513,39 +1491,45 @@
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>MH-MUM-Cloud FC Chembur</t>
+          <t>TG-HYD-Express Outlet Manikonda</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 5)</t>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="4" t="inlineStr"/>
+      <c r="A40" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Express Outlet Sainikpuri</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1554,21 +1538,31 @@
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="4" t="inlineStr"/>
+      <c r="A41" s="4" t="n">
+        <v>16</v>
+      </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="8" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>MUM</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>MH-MUM-Cloud FC Borivali</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
@@ -1591,11 +1585,11 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+          <t>Assorted French Macarons (Pack Of 5)</t>
         </is>
       </c>
     </row>
@@ -1614,100 +1608,209 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Signature Belgium Chocolate Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="8" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Italian Tiramisu Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="4" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="8" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Danish Hazelnut Chocolate Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="inlineStr"/>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="8" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="4" t="inlineStr"/>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="8" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Harley's Spl. Classic Russian Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="8" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>Pack Of 9 Medoviks And 6 Macarons</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="4" t="n">
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>MH-MUM-Express Outlet Jio World</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Italian Tiramisu Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>MH-MUM-Express Outlet Jio World</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr"/>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>MH-MUM-Express Outlet Palladium</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>Italian Cappuccino</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>PUN</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>MH-PUN-Cloud FC Tathewadi</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>Harley's Special Mawa Bar Cake (250 Gms)</t>
         </is>
@@ -2028,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2054,7 +2157,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Total Items with OOS: 12</t>
+          <t>Total Items with OOS: 14</t>
         </is>
       </c>
       <c r="E1" s="2" t="n"/>
@@ -2166,12 +2269,12 @@
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>KA-BLR-Cloud FC Basaveshwara Nagar</t>
+          <t>KA-BLR-Cloud FC Bellandur</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
@@ -2179,36 +2282,30 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 5)</t>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="A6" s="4" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>KA-BLR-Cloud FC Electronic City</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Signature Belgium Chocolate Medovik With Macaron</t>
+          <t>Assorted Medoviks (Pack Of 6)</t>
         </is>
       </c>
     </row>
@@ -2223,15 +2320,15 @@
       <c r="D7" s="8" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Danish Hazelnut Chocolate Medovik With Macaron</t>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
         </is>
       </c>
     </row>
@@ -2246,67 +2343,67 @@
       <c r="D8" s="8" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
+          <t>Harley's Signatures (Pack of 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
           <t>Pack Of 4 Medoviks And 4 Macarons</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>KA-BLR-Cloud FC Malleshwaram</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>KA-BLR-Cloud FC Malleshwaram</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Assorted Cheesecakes (Pack Of 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
         </is>
       </c>
     </row>
@@ -2325,46 +2422,40 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Italian Tiramisu Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>KA-BLR-Cloud FC Sarjapur</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2374,41 +2465,99 @@
       <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr">
         <is>
+          <t>KA-BLR-Cloud FC Nagawara</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>KA-BLR-Cloud FC Whitefield</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Assorted French Macarons (Pack Of 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
           <t>KA-BLR-Ivory Lounge JP Nagar</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Assorted French Macarons (Pack Of 5)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
@@ -2425,7 +2574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2446,12 +2595,12 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Total Outlets: 6</t>
+          <t>Total Outlets: 7</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Total Items with OOS: 12</t>
+          <t>Total Items with OOS: 15</t>
         </is>
       </c>
       <c r="E1" s="2" t="n"/>
@@ -2520,11 +2669,11 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
@@ -2543,63 +2692,63 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Lotus Biscoff Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>TG-HYD-Cloud FC Charminar</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="F6" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
@@ -2618,11 +2767,11 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Lotus Biscoff Cheesecake With Macaron</t>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
         </is>
       </c>
     </row>
@@ -2641,40 +2790,34 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Assorted Cheesecakes (Pack Of 12)</t>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="A9" s="4" t="inlineStr"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Cloud FC Habsiguda</t>
-        </is>
-      </c>
+      <c r="D9" s="8" t="inlineStr"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+          <t>Lotus Biscoff Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
@@ -2693,88 +2836,82 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Assorted Cheesecakes (Pack Of 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Cloud FC Habsiguda</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Assorted Cheesecakes (Pack Of 6)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>18</v>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Express Outlet Madhapur</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>TG-HYD-Express Outlet Manikonda</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>15</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -2784,7 +2921,7 @@
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2794,18 +2931,105 @@
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr">
         <is>
+          <t>TG-HYD-Express Outlet Kapil Tower</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Assorted Cheesecakes (Pack Of 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Express Outlet Madhapur</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Italian Tiramisu Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TG-HYD-Express Outlet Manikonda</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
           <t>TG-HYD-Express Outlet Sainikpuri</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Assorted French Macarons (Pack Of 12)</t>
         </is>
@@ -2843,7 +3067,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Total Outlets: 5</t>
+          <t>Total Outlets: 2</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -2908,7 +3132,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>MH-MUM-Cloud FC BKC</t>
+          <t>MH-MUM-Cloud FC Borivali</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -2917,29 +3141,23 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 24)</t>
+          <t>Pack Of 4 Medoviks And 4 Macarons</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="A4" s="4" t="inlineStr"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>MH-MUM-Cloud FC Borivali</t>
-        </is>
-      </c>
+      <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
@@ -2978,31 +3196,25 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="A6" s="4" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>MH-MUM-Cloud FC Chembur</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 5)</t>
+          <t>Signature Belgium Chocolate Medovik With Macaron</t>
         </is>
       </c>
     </row>
@@ -3021,11 +3233,11 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Assorted French Macarons (Pack Of 12)</t>
+          <t>Italian Tiramisu Medovik With Macaron</t>
         </is>
       </c>
     </row>
@@ -3044,11 +3256,11 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Pack Of 4 Medoviks And 4 Macarons</t>
+          <t>Danish Hazelnut Chocolate Medovik With Macaron</t>
         </is>
       </c>
     </row>
@@ -3067,11 +3279,11 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
+          <t>Chef's Favourite Blueberry Cheesecake With Macaron</t>
         </is>
       </c>
     </row>
@@ -3090,46 +3302,40 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Harley's Spl. Classic Russian Medovik With Macaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Pack Of 9 Medoviks And 6 Macarons</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>MH-MUM-Express Outlet Jio World</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Italian Tiramisu Medovik With Macaron</t>
+          <t>Pack Of 4 Cheesecakes And 4 Macarons</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -3139,7 +3345,7 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>MH-MUM-Express Outlet Palladium</t>
+          <t>MH-MUM-Express Outlet Jio World</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3148,11 +3354,11 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Italian Cappuccino</t>
+          <t>Italian Tiramisu Medovik With Macaron</t>
         </is>
       </c>
     </row>
